--- a/artfynd/A 53121-2022 artfynd.xlsx
+++ b/artfynd/A 53121-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53121-2022 artfynd.xlsx
+++ b/artfynd/A 53121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108363297</v>
+        <v>108364104</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,13 +711,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574320.2530940812</v>
+        <v>574325</v>
       </c>
       <c r="R2" t="n">
-        <v>7013893.4997139</v>
+        <v>7013906</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108361922</v>
+        <v>108363297</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574459.4079173917</v>
+        <v>574320</v>
       </c>
       <c r="R3" t="n">
-        <v>7013887.247715793</v>
+        <v>7013893</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108361511</v>
+        <v>108363951</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574466.9166226649</v>
+        <v>574325</v>
       </c>
       <c r="R4" t="n">
-        <v>7013933.394181789</v>
+        <v>7013906</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108362806</v>
+        <v>108361206</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,17 +1031,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Prästflon, Ång</t>
+          <t>Prästflons naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574399.4021785191</v>
+        <v>574473</v>
       </c>
       <c r="R5" t="n">
-        <v>7013886.312176081</v>
+        <v>7013952</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108363951</v>
+        <v>108361339</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,35 +1118,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Prästflon, Ång</t>
+          <t>Prästflons naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574325.344028262</v>
+        <v>574477</v>
       </c>
       <c r="R6" t="n">
-        <v>7013907.589329534</v>
+        <v>7013943</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,19 +1215,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108362678</v>
+        <v>108361511</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1281,13 +1251,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574431.6691289669</v>
+        <v>574466</v>
       </c>
       <c r="R7" t="n">
-        <v>7013876.690942556</v>
+        <v>7013933</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,59 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108364418</v>
+        <v>108361922</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574248.6540818319</v>
+        <v>574460</v>
       </c>
       <c r="R8" t="n">
-        <v>7013886.440249336</v>
+        <v>7013888</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,37 +1431,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108363802</v>
+        <v>108362678</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574324.4210641993</v>
+        <v>574431</v>
       </c>
       <c r="R9" t="n">
-        <v>7013908.469465317</v>
+        <v>7013877</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1547,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,19 +1539,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108362983</v>
+        <v>108362806</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1625,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574369.7132427807</v>
+        <v>574399</v>
       </c>
       <c r="R10" t="n">
-        <v>7013882.020970003</v>
+        <v>7013887</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1660,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,56 +1647,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108364827</v>
+        <v>108362983</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574147.6814372464</v>
+        <v>574370</v>
       </c>
       <c r="R11" t="n">
-        <v>7013802.534148169</v>
+        <v>7013882</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1778,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,26 +1748,21 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren, Erik Christiansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108361339</v>
+        <v>108363077</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1852,14 +1787,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Prästflons naturreservat, Ång</t>
+          <t>Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574476.611419509</v>
+        <v>574347</v>
       </c>
       <c r="R12" t="n">
-        <v>7013943.533926502</v>
+        <v>7013866</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1891,7 +1826,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1836,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,16 +1866,11 @@
         <v>108364237</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1969,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574288.5520256122</v>
+        <v>574288</v>
       </c>
       <c r="R13" t="n">
-        <v>7013898.177169512</v>
+        <v>7013898</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2044,12 +1974,7 @@
         <v>108363748</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574324.4418488162</v>
+        <v>574324</v>
       </c>
       <c r="R14" t="n">
-        <v>7013907.568516403</v>
+        <v>7013908</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2154,37 +2079,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108363077</v>
+        <v>108362387</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2195,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574346.6202252172</v>
+        <v>574479</v>
       </c>
       <c r="R15" t="n">
-        <v>7013865.712814141</v>
+        <v>7013855</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2230,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,37 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108364104</v>
+        <v>108363802</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574325.3648131354</v>
+        <v>574324</v>
       </c>
       <c r="R16" t="n">
-        <v>7013906.688380371</v>
+        <v>7013908</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2343,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,12 +2298,7 @@
         <v>108362056</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2426,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574454.0711215877</v>
+        <v>574455</v>
       </c>
       <c r="R17" t="n">
-        <v>7013903.350188786</v>
+        <v>7013903</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -2495,6 +2405,232 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>108364418</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>574249</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7013887</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>108364827</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>574148</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7013802</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren, Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53121-2022 artfynd.xlsx
+++ b/artfynd/A 53121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108364104</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108363297</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108363951</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361339</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361511</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108361922</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108362678</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108362806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108362983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108363077</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108364237</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,6 +2141,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108363748</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108362387</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108363802</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108362056</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2518,6 +2603,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108364418</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,8 +2721,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108364827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>